--- a/figures/dataset_CLV.xlsx
+++ b/figures/dataset_CLV.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.martet\Documents\Agrostat Dijon\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2EF3F80-E526-462F-8DC4-9FC840C5837E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FEAA8D-1D0E-42B3-8A2F-479A6D4CC779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="CLV" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>Région</t>
   </si>
@@ -76,13 +77,373 @@
   </si>
   <si>
     <t>cluster 2</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Variable name</t>
+  </si>
+  <si>
+    <t>fPC1 interpretation</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>AMR_ville_FQ_R</t>
+  </si>
+  <si>
+    <t>AMC</t>
+  </si>
+  <si>
+    <t>log_AMC_ville_FQ</t>
+  </si>
+  <si>
+    <t>log_AMC_ES_FQ</t>
+  </si>
+  <si>
+    <t>Humans</t>
+  </si>
+  <si>
+    <t>medecin_hab</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>veto_by_AC</t>
+  </si>
+  <si>
+    <t>log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t>AMR_animaux_compagnie_FQ_R</t>
+  </si>
+  <si>
+    <t>AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>air_PM25</t>
+  </si>
+  <si>
+    <t>dju_refroi</t>
+  </si>
+  <si>
+    <t>fPC1 % var</t>
+  </si>
+  <si>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>93.1%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EQI_st</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (European quality of government index)</t>
+    </r>
+  </si>
+  <si>
+    <t>81.3%</t>
+  </si>
+  <si>
+    <t>76.9%</t>
+  </si>
+  <si>
+    <t>92.4%</t>
+  </si>
+  <si>
+    <t>85.8%</t>
+  </si>
+  <si>
+    <t>91.1%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Consumption of Fluoroquinolone in primary care setting over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: PACA, Occitanie ↑ VS Bretagne, Pays de la Loire ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Consumption of Fluoroquinolone in hospitals over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Grand-Est, PACA, Occitanie ↑ VS Bretagne, Pays de la Loire ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Citizens’ trust in the quality, impartiality, and reliability of public institutions over the time:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bretagne ↑ VS PACA ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Number of doctors per population over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: PACA, IDF ↑ VS Normandie, Centre-Val de Loire, Hauts-de-France↓ </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fluoroquinolone resistance in pets over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: PACA, IDF ↑ VS Centre-Val de Loire ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Number of vet per pet over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Bretagne ↑ VS Hauts-de-France, Centre Val-de-loire ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Livestock density over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Bretagne ↑ VS IDF ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fluoroquinolone resistance in livestock over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Occitanie ↑ VS all other regions ↓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Proportion of fine particles measuring 2.5 micrometers over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Hauts-de-France, IDF ↑ VS Bretagne, Nouvelle-Aquitaine ↓</t>
+    </r>
+  </si>
+  <si>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accumulated difference between daily outdoor temperatures and a reference temperature above which cooling is needed over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: PACA, Occitanie ↑ VS Bretagne, Normandie ↓</t>
+    </r>
+  </si>
+  <si>
+    <t>92.8%</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Fluoroquinolone resistance in primary care setting over the time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: PACA ↑ VS Centre-Val-de-Loire ↓</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,8 +451,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -113,6 +482,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFACC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8766D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3A500"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE76BF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00BF7D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -181,17 +580,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -207,11 +612,80 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -221,6 +695,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00BF7D"/>
+      <color rgb="FF00B0F6"/>
+      <color rgb="FFE76BF3"/>
+      <color rgb="FFA3A500"/>
+      <color rgb="FFF8766D"/>
       <color rgb="FFFFFACC"/>
       <color rgb="FF00AC8C"/>
     </mruColors>
@@ -534,251 +1013,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27BBFA5-915D-4CED-936B-1A2746899247}">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I6" s="2" t="s">
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="J6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -792,4 +1271,183 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00E3398-53EF-4F84-88FD-DB80C001C280}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="22"/>
+      <c r="B6" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0.99</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="32">
+        <v>1</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/figures/dataset_CLV.xlsx
+++ b/figures/dataset_CLV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.martet\Documents\Agrostat Dijon\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FEAA8D-1D0E-42B3-8A2F-479A6D4CC779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73208110-5D93-43C9-B090-86D2FF109AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
   </bookViews>
   <sheets>
     <sheet name="CLV" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
   <si>
     <t>Région</t>
   </si>
@@ -460,7 +460,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,6 +512,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00BF7D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -597,6 +603,72 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -612,81 +684,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,29 +1022,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27BBFA5-915D-4CED-936B-1A2746899247}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="I1" s="7" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="I1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,7 +1100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1119,7 +1129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1148,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1159,29 +1169,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="31"/>
+      <c r="D9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,7 +1231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,7 +1251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1261,8 +1271,113 @@
         <v>9</v>
       </c>
     </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:C9"/>
@@ -1276,167 +1391,167 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C00E3398-53EF-4F84-88FD-DB80C001C280}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="18" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
-      <c r="B6" s="26" t="s">
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="36"/>
+      <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="20">
         <v>0.99</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29" t="s">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29" t="s">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="37"/>
+      <c r="B9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="24">
         <v>1</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29" t="s">
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="37"/>
+      <c r="B10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
+    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34" t="s">
+    <row r="12" spans="1:4" ht="68.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="38"/>
+      <c r="B12" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="28" t="s">
         <v>50</v>
       </c>
     </row>

--- a/figures/dataset_CLV.xlsx
+++ b/figures/dataset_CLV.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\g.martet\Documents\Agrostat Dijon\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73208110-5D93-43C9-B090-86D2FF109AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9D79F1-BF8B-4B4B-8C3D-F998682E67E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E12FFB58-BF93-4D82-9450-4001AA5E4D95}"/>
   </bookViews>
   <sheets>
     <sheet name="CLV" sheetId="1" r:id="rId1"/>
     <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="result_CLV" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="80">
   <si>
     <t>Région</t>
   </si>
@@ -437,13 +438,211 @@
       </rPr>
       <t>: PACA ↑ VS Centre-Val-de-Loire ↓</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>fPC1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <t>cluster1</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>number of variables</t>
+  </si>
+  <si>
+    <t>variable retained</t>
+  </si>
+  <si>
+    <t>Initial number of variables</t>
+  </si>
+  <si>
+    <t>Hospitals Fluoroquinolone cunsomption</t>
+  </si>
+  <si>
+    <t>cluster 3</t>
+  </si>
+  <si>
+    <t>cluster 4</t>
+  </si>
+  <si>
+    <t>Primary care setting Fluoroquinolone cunsumption</t>
+  </si>
+  <si>
+    <t>Livestock Fluoroquinolone resistance</t>
+  </si>
+  <si>
+    <t>Pets Fluoroquinolone resistance</t>
+  </si>
+  <si>
+    <t>number of vet by pets</t>
+  </si>
+  <si>
+    <t>Livestock density</t>
+  </si>
+  <si>
+    <t>number of cluster (K) = Final number of variables</t>
+  </si>
+  <si>
+    <t>Cooling degree days</t>
+  </si>
+  <si>
+    <t>Fine particulate matter (PM 2.5 µm) proportion</t>
+  </si>
+  <si>
+    <t>European Quality of government Index (EQI)</t>
+  </si>
+  <si>
+    <t>number of doctors per capita</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,8 +658,67 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Marianne"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,6 +776,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -666,6 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -696,7 +961,74 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,13 +1037,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE76BF3"/>
       <color rgb="FF00BF7D"/>
       <color rgb="FF00B0F6"/>
-      <color rgb="FFE76BF3"/>
       <color rgb="FFA3A500"/>
+      <color rgb="FF00AC8C"/>
       <color rgb="FFF8766D"/>
       <color rgb="FFFFFACC"/>
-      <color rgb="FF00AC8C"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1022,29 +1354,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27BBFA5-915D-4CED-936B-1A2746899247}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="24" width="5.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="I1" s="29" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="I1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="O1" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+    </row>
+    <row r="2" spans="1:24" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1070,8 +1415,38 @@
       <c r="K2" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1474,38 @@
       <c r="K3" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1128,8 +1533,38 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1157,8 +1592,38 @@
       <c r="K5" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,29 +1634,57 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="O8" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32" t="s">
+      <c r="C9" s="32"/>
+      <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E9" s="34"/>
+      <c r="F9" s="35"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+    </row>
+    <row r="10" spans="1:24" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1210,8 +1703,38 @@
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,8 +1753,38 @@
       <c r="F11" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1250,8 +1803,38 @@
       <c r="F12" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1270,111 +1853,299 @@
       <c r="F13" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="O13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="O16" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32" t="s">
+      <c r="C17" s="32"/>
+      <c r="D17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="34"/>
+      <c r="F17" s="35"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" s="41"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="W17" s="40"/>
+      <c r="X17" s="40"/>
+    </row>
+    <row r="18" spans="1:24" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="29" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="29" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="O18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q18" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="R18" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="S18" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U18" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="V18" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="W18" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="X18" s="42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="39" t="s">
+      <c r="C19" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F19" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="R19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="V19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="W19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="X19" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="39" t="s">
+      <c r="C20" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F20" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="R20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="S20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="V20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="W20" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="X20" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="39" t="s">
+      <c r="C21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="29" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="R21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="S21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="U21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="V21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="W21" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="X21" s="42" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="17">
+    <mergeCell ref="O16:X16"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="O1:X1"/>
+    <mergeCell ref="O8:X8"/>
+    <mergeCell ref="P9:R9"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="S9:U9"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:F17"/>
@@ -1382,9 +2153,10 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1428,7 +2200,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1442,7 +2214,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="13" t="s">
         <v>20</v>
       </c>
@@ -1454,7 +2226,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="37" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -1468,7 +2240,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="36"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
@@ -1480,7 +2252,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="38" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -1494,7 +2266,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="21" t="s">
         <v>24</v>
       </c>
@@ -1506,7 +2278,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="21" t="s">
         <v>25</v>
       </c>
@@ -1518,7 +2290,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="21" t="s">
         <v>27</v>
       </c>
@@ -1530,7 +2302,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="25" t="s">
@@ -1544,7 +2316,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="68.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38"/>
+      <c r="A12" s="39"/>
       <c r="B12" s="25" t="s">
         <v>30</v>
       </c>
@@ -1565,4 +2337,228 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4185D1A-A5C3-48A4-ADE6-75ABECE355A2}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="86.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A2" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="48">
+        <v>24</v>
+      </c>
+      <c r="C2" s="48">
+        <v>2</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="56">
+        <v>18</v>
+      </c>
+      <c r="F2" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="43"/>
+    </row>
+    <row r="3" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="56">
+        <v>6</v>
+      </c>
+      <c r="F3" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="43"/>
+    </row>
+    <row r="4" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A4" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="50">
+        <v>19</v>
+      </c>
+      <c r="C4" s="50">
+        <v>4</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="58">
+        <v>5</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="43"/>
+    </row>
+    <row r="5" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A5" s="49"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="58">
+        <v>3</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A6" s="49"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="58">
+        <v>2</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="43"/>
+    </row>
+    <row r="7" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A7" s="49"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="58">
+        <v>9</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="44"/>
+    </row>
+    <row r="8" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A8" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="52">
+        <v>7</v>
+      </c>
+      <c r="C8" s="52">
+        <v>2</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="60">
+        <v>3</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="60">
+        <v>4</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A10" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="54">
+        <v>11</v>
+      </c>
+      <c r="C10" s="54">
+        <v>2</v>
+      </c>
+      <c r="D10" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="62">
+        <v>3</v>
+      </c>
+      <c r="F10" s="66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="27.75" x14ac:dyDescent="0.5">
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="62">
+        <v>8</v>
+      </c>
+      <c r="F11" s="66" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>